--- a/artfynd/A 9057-2026 artfynd.xlsx
+++ b/artfynd/A 9057-2026 artfynd.xlsx
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134215452</v>
+        <v>134215471</v>
       </c>
       <c r="B6" t="n">
-        <v>91971</v>
+        <v>79358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464271</v>
+        <v>464264</v>
       </c>
       <c r="R6" t="n">
-        <v>7073972</v>
+        <v>7074102</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1139,6 +1139,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1165,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134215471</v>
+        <v>134215452</v>
       </c>
       <c r="B7" t="n">
-        <v>79358</v>
+        <v>91971</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464264</v>
+        <v>464271</v>
       </c>
       <c r="R7" t="n">
-        <v>7074102</v>
+        <v>7073972</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1236,11 +1241,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -2349,7 +2349,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134215473</v>
+        <v>134215468</v>
       </c>
       <c r="B19" t="n">
         <v>79358</v>
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>464149</v>
+        <v>464338</v>
       </c>
       <c r="R19" t="n">
-        <v>7074035</v>
+        <v>7073993</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2451,7 +2451,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134215468</v>
+        <v>134215473</v>
       </c>
       <c r="B20" t="n">
         <v>79358</v>
@@ -2486,10 +2486,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464338</v>
+        <v>464149</v>
       </c>
       <c r="R20" t="n">
-        <v>7073993</v>
+        <v>7074035</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 9057-2026 artfynd.xlsx
+++ b/artfynd/A 9057-2026 artfynd.xlsx
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134215471</v>
+        <v>134215452</v>
       </c>
       <c r="B6" t="n">
-        <v>79358</v>
+        <v>91971</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464264</v>
+        <v>464271</v>
       </c>
       <c r="R6" t="n">
-        <v>7074102</v>
+        <v>7073972</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1139,11 +1139,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1170,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134215452</v>
+        <v>134215471</v>
       </c>
       <c r="B7" t="n">
-        <v>91971</v>
+        <v>79358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464271</v>
+        <v>464264</v>
       </c>
       <c r="R7" t="n">
-        <v>7073972</v>
+        <v>7074102</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1241,6 +1236,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 9057-2026 artfynd.xlsx
+++ b/artfynd/A 9057-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134215459</v>
       </c>
       <c r="B2" t="n">
-        <v>91971</v>
+        <v>91973</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>134215467</v>
       </c>
       <c r="B3" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>134215456</v>
       </c>
       <c r="B4" t="n">
-        <v>91971</v>
+        <v>91973</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>134215461</v>
       </c>
       <c r="B5" t="n">
-        <v>91971</v>
+        <v>91973</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134215452</v>
+        <v>134215471</v>
       </c>
       <c r="B6" t="n">
-        <v>91971</v>
+        <v>79359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464271</v>
+        <v>464264</v>
       </c>
       <c r="R6" t="n">
-        <v>7073972</v>
+        <v>7074102</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1139,6 +1139,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1165,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134215471</v>
+        <v>134215452</v>
       </c>
       <c r="B7" t="n">
-        <v>79358</v>
+        <v>91973</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464264</v>
+        <v>464271</v>
       </c>
       <c r="R7" t="n">
-        <v>7074102</v>
+        <v>7073972</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1236,11 +1241,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134215453</v>
+        <v>134215446</v>
       </c>
       <c r="B8" t="n">
-        <v>91971</v>
+        <v>91959</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464285</v>
+        <v>464180</v>
       </c>
       <c r="R8" t="n">
-        <v>7073959</v>
+        <v>7074075</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134215446</v>
+        <v>134215453</v>
       </c>
       <c r="B9" t="n">
-        <v>91957</v>
+        <v>91973</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464180</v>
+        <v>464285</v>
       </c>
       <c r="R9" t="n">
-        <v>7074075</v>
+        <v>7073959</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1464,7 +1464,7 @@
         <v>134215476</v>
       </c>
       <c r="B10" t="n">
-        <v>83207</v>
+        <v>83208</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>134215447</v>
       </c>
       <c r="B11" t="n">
-        <v>80474</v>
+        <v>80475</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>134215458</v>
       </c>
       <c r="B12" t="n">
-        <v>91971</v>
+        <v>91973</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>134215454</v>
       </c>
       <c r="B13" t="n">
-        <v>91971</v>
+        <v>91973</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>134215472</v>
       </c>
       <c r="B14" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>134215448</v>
       </c>
       <c r="B15" t="n">
-        <v>80474</v>
+        <v>80475</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>134215475</v>
       </c>
       <c r="B16" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>134215469</v>
       </c>
       <c r="B17" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>134215450</v>
       </c>
       <c r="B18" t="n">
-        <v>91971</v>
+        <v>91973</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>134215468</v>
       </c>
       <c r="B19" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>134215473</v>
       </c>
       <c r="B20" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>134215474</v>
       </c>
       <c r="B21" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>134215455</v>
       </c>
       <c r="B22" t="n">
-        <v>91971</v>
+        <v>91973</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>134215449</v>
       </c>
       <c r="B23" t="n">
-        <v>79517</v>
+        <v>79518</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>134215457</v>
       </c>
       <c r="B24" t="n">
-        <v>91971</v>
+        <v>91973</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 9057-2026 artfynd.xlsx
+++ b/artfynd/A 9057-2026 artfynd.xlsx
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134215471</v>
+        <v>134215452</v>
       </c>
       <c r="B6" t="n">
-        <v>79359</v>
+        <v>91973</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464264</v>
+        <v>464271</v>
       </c>
       <c r="R6" t="n">
-        <v>7074102</v>
+        <v>7073972</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1139,11 +1139,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1170,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134215452</v>
+        <v>134215471</v>
       </c>
       <c r="B7" t="n">
-        <v>91973</v>
+        <v>79359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464271</v>
+        <v>464264</v>
       </c>
       <c r="R7" t="n">
-        <v>7073972</v>
+        <v>7074102</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1241,6 +1236,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134215446</v>
+        <v>134215453</v>
       </c>
       <c r="B8" t="n">
-        <v>91959</v>
+        <v>91973</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464180</v>
+        <v>464285</v>
       </c>
       <c r="R8" t="n">
-        <v>7074075</v>
+        <v>7073959</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134215453</v>
+        <v>134215446</v>
       </c>
       <c r="B9" t="n">
-        <v>91973</v>
+        <v>91959</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464285</v>
+        <v>464180</v>
       </c>
       <c r="R9" t="n">
-        <v>7073959</v>
+        <v>7074075</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 9057-2026 artfynd.xlsx
+++ b/artfynd/A 9057-2026 artfynd.xlsx
@@ -874,7 +874,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134215461</v>
+        <v>134215456</v>
       </c>
       <c r="B4" t="n">
         <v>91974</v>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464226</v>
+        <v>464419</v>
       </c>
       <c r="R4" t="n">
-        <v>7074144</v>
+        <v>7073960</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,7 +971,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134215456</v>
+        <v>134215461</v>
       </c>
       <c r="B5" t="n">
         <v>91974</v>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464419</v>
+        <v>464226</v>
       </c>
       <c r="R5" t="n">
-        <v>7073960</v>
+        <v>7074144</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134215453</v>
+        <v>134215446</v>
       </c>
       <c r="B8" t="n">
-        <v>91974</v>
+        <v>91960</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464285</v>
+        <v>464180</v>
       </c>
       <c r="R8" t="n">
-        <v>7073959</v>
+        <v>7074075</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134215446</v>
+        <v>134215453</v>
       </c>
       <c r="B9" t="n">
-        <v>91960</v>
+        <v>91974</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464180</v>
+        <v>464285</v>
       </c>
       <c r="R9" t="n">
-        <v>7074075</v>
+        <v>7073959</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1849,10 +1849,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134215472</v>
+        <v>134215448</v>
       </c>
       <c r="B14" t="n">
-        <v>79359</v>
+        <v>80475</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,21 +1860,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>464167</v>
+        <v>464144</v>
       </c>
       <c r="R14" t="n">
-        <v>7073990</v>
+        <v>7073965</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1920,11 +1920,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1951,7 +1946,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134215475</v>
+        <v>134215472</v>
       </c>
       <c r="B15" t="n">
         <v>79359</v>
@@ -1986,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>464223</v>
+        <v>464167</v>
       </c>
       <c r="R15" t="n">
-        <v>7074141</v>
+        <v>7073990</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2053,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134215448</v>
+        <v>134215475</v>
       </c>
       <c r="B16" t="n">
-        <v>80475</v>
+        <v>79359</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2064,21 +2059,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2088,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464144</v>
+        <v>464223</v>
       </c>
       <c r="R16" t="n">
-        <v>7073965</v>
+        <v>7074141</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2124,6 +2119,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 9057-2026 artfynd.xlsx
+++ b/artfynd/A 9057-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134215459</v>
       </c>
       <c r="B2" t="n">
-        <v>91974</v>
+        <v>91981</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>134215467</v>
       </c>
       <c r="B3" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>134215456</v>
       </c>
       <c r="B4" t="n">
-        <v>91974</v>
+        <v>91981</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>134215461</v>
       </c>
       <c r="B5" t="n">
-        <v>91974</v>
+        <v>91981</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>134215452</v>
       </c>
       <c r="B6" t="n">
-        <v>91974</v>
+        <v>91981</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>134215471</v>
       </c>
       <c r="B7" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134215446</v>
+        <v>134215453</v>
       </c>
       <c r="B8" t="n">
-        <v>91960</v>
+        <v>91981</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464180</v>
+        <v>464285</v>
       </c>
       <c r="R8" t="n">
-        <v>7074075</v>
+        <v>7073959</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134215453</v>
+        <v>134215446</v>
       </c>
       <c r="B9" t="n">
-        <v>91974</v>
+        <v>91967</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464285</v>
+        <v>464180</v>
       </c>
       <c r="R9" t="n">
-        <v>7073959</v>
+        <v>7074075</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1464,7 +1464,7 @@
         <v>134215476</v>
       </c>
       <c r="B10" t="n">
-        <v>83208</v>
+        <v>83215</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>134215447</v>
       </c>
       <c r="B11" t="n">
-        <v>80475</v>
+        <v>80482</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>134215458</v>
       </c>
       <c r="B12" t="n">
-        <v>91974</v>
+        <v>91981</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>134215454</v>
       </c>
       <c r="B13" t="n">
-        <v>91974</v>
+        <v>91981</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>134215448</v>
       </c>
       <c r="B14" t="n">
-        <v>80475</v>
+        <v>80482</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1946,10 +1946,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134215472</v>
+        <v>134215475</v>
       </c>
       <c r="B15" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>464167</v>
+        <v>464223</v>
       </c>
       <c r="R15" t="n">
-        <v>7073990</v>
+        <v>7074141</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134215475</v>
+        <v>134215472</v>
       </c>
       <c r="B16" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464223</v>
+        <v>464167</v>
       </c>
       <c r="R16" t="n">
-        <v>7074141</v>
+        <v>7073990</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2153,7 +2153,7 @@
         <v>134215469</v>
       </c>
       <c r="B17" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>134215450</v>
       </c>
       <c r="B18" t="n">
-        <v>91974</v>
+        <v>91981</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>134215468</v>
       </c>
       <c r="B19" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>134215473</v>
       </c>
       <c r="B20" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>134215474</v>
       </c>
       <c r="B21" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>134215455</v>
       </c>
       <c r="B22" t="n">
-        <v>91974</v>
+        <v>91981</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>134215449</v>
       </c>
       <c r="B23" t="n">
-        <v>79518</v>
+        <v>79525</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>134215457</v>
       </c>
       <c r="B24" t="n">
-        <v>91974</v>
+        <v>91981</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 9057-2026 artfynd.xlsx
+++ b/artfynd/A 9057-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134215459</v>
+        <v>134215446</v>
       </c>
       <c r="B2" t="n">
-        <v>91981</v>
+        <v>91974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464239</v>
+        <v>464180</v>
       </c>
       <c r="R2" t="n">
-        <v>7074054</v>
+        <v>7074075</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134215467</v>
+        <v>134215450</v>
       </c>
       <c r="B3" t="n">
-        <v>79366</v>
+        <v>91988</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>464342</v>
+        <v>464299</v>
       </c>
       <c r="R3" t="n">
-        <v>7074061</v>
+        <v>7074011</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,14 +869,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134215456</v>
+        <v>134215452</v>
       </c>
       <c r="B4" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464419</v>
+        <v>464271</v>
       </c>
       <c r="R4" t="n">
-        <v>7073960</v>
+        <v>7073972</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,14 +966,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134215461</v>
+        <v>134215453</v>
       </c>
       <c r="B5" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464226</v>
+        <v>464285</v>
       </c>
       <c r="R5" t="n">
-        <v>7074144</v>
+        <v>7073959</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,14 +1063,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134215452</v>
+        <v>134215454</v>
       </c>
       <c r="B6" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464271</v>
+        <v>464304</v>
       </c>
       <c r="R6" t="n">
-        <v>7073972</v>
+        <v>7073965</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134215471</v>
+        <v>134215455</v>
       </c>
       <c r="B7" t="n">
-        <v>79366</v>
+        <v>91988</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464264</v>
+        <v>464436</v>
       </c>
       <c r="R7" t="n">
-        <v>7074102</v>
+        <v>7073960</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1236,11 +1231,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,14 +1257,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134215453</v>
+        <v>134215456</v>
       </c>
       <c r="B8" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1302,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464285</v>
+        <v>464419</v>
       </c>
       <c r="R8" t="n">
-        <v>7073959</v>
+        <v>7073960</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134215446</v>
+        <v>134215457</v>
       </c>
       <c r="B9" t="n">
-        <v>91967</v>
+        <v>91988</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464180</v>
+        <v>464412</v>
       </c>
       <c r="R9" t="n">
-        <v>7074075</v>
+        <v>7073969</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134215476</v>
+        <v>134215458</v>
       </c>
       <c r="B10" t="n">
-        <v>83215</v>
+        <v>91988</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464141</v>
+        <v>464232</v>
       </c>
       <c r="R10" t="n">
-        <v>7074038</v>
+        <v>7073957</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1558,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134215447</v>
+        <v>134215459</v>
       </c>
       <c r="B11" t="n">
-        <v>80482</v>
+        <v>91988</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464232</v>
+        <v>464239</v>
       </c>
       <c r="R11" t="n">
-        <v>7073942</v>
+        <v>7074054</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1655,14 +1645,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134215458</v>
+        <v>134215461</v>
       </c>
       <c r="B12" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1690,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>464232</v>
+        <v>464226</v>
       </c>
       <c r="R12" t="n">
-        <v>7073957</v>
+        <v>7074144</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1752,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134215454</v>
+        <v>134215449</v>
       </c>
       <c r="B13" t="n">
-        <v>91981</v>
+        <v>79532</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>1249</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464304</v>
+        <v>464160</v>
       </c>
       <c r="R13" t="n">
-        <v>7073965</v>
+        <v>7074048</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1849,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134215448</v>
+        <v>134215476</v>
       </c>
       <c r="B14" t="n">
-        <v>80482</v>
+        <v>83222</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1884,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>464144</v>
+        <v>464141</v>
       </c>
       <c r="R14" t="n">
-        <v>7073965</v>
+        <v>7074038</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1946,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134215475</v>
+        <v>134215447</v>
       </c>
       <c r="B15" t="n">
-        <v>79366</v>
+        <v>80489</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1957,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1981,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>464223</v>
+        <v>464232</v>
       </c>
       <c r="R15" t="n">
-        <v>7074141</v>
+        <v>7073942</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2017,11 +2007,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2048,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134215472</v>
+        <v>134215448</v>
       </c>
       <c r="B16" t="n">
-        <v>79366</v>
+        <v>80489</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2059,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2083,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464167</v>
+        <v>464144</v>
       </c>
       <c r="R16" t="n">
-        <v>7073990</v>
+        <v>7073965</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2119,11 +2104,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2150,14 +2130,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134215469</v>
+        <v>134215467</v>
       </c>
       <c r="B17" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2185,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>464302</v>
+        <v>464342</v>
       </c>
       <c r="R17" t="n">
-        <v>7073940</v>
+        <v>7074061</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2252,32 +2232,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134215450</v>
+        <v>134215468</v>
       </c>
       <c r="B18" t="n">
-        <v>91981</v>
+        <v>79373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2287,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464299</v>
+        <v>464338</v>
       </c>
       <c r="R18" t="n">
-        <v>7074011</v>
+        <v>7073993</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2323,6 +2303,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2349,14 +2334,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134215468</v>
+        <v>134215469</v>
       </c>
       <c r="B19" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2384,10 +2369,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>464338</v>
+        <v>464302</v>
       </c>
       <c r="R19" t="n">
-        <v>7073993</v>
+        <v>7073940</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2451,14 +2436,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134215473</v>
+        <v>134215471</v>
       </c>
       <c r="B20" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2486,10 +2471,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464149</v>
+        <v>464264</v>
       </c>
       <c r="R20" t="n">
-        <v>7074035</v>
+        <v>7074102</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2553,14 +2538,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134215474</v>
+        <v>134215472</v>
       </c>
       <c r="B21" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2588,10 +2573,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464190</v>
+        <v>464167</v>
       </c>
       <c r="R21" t="n">
-        <v>7074068</v>
+        <v>7073990</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2655,32 +2640,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134215455</v>
+        <v>134215473</v>
       </c>
       <c r="B22" t="n">
-        <v>91981</v>
+        <v>79373</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2690,10 +2675,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>464436</v>
+        <v>464149</v>
       </c>
       <c r="R22" t="n">
-        <v>7073960</v>
+        <v>7074035</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2726,6 +2711,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2752,10 +2742,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134215449</v>
+        <v>134215474</v>
       </c>
       <c r="B23" t="n">
-        <v>79525</v>
+        <v>79373</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2763,21 +2753,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1249</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2787,10 +2777,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>464160</v>
+        <v>464190</v>
       </c>
       <c r="R23" t="n">
-        <v>7074048</v>
+        <v>7074068</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2823,6 +2813,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2849,32 +2844,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134215457</v>
+        <v>134215475</v>
       </c>
       <c r="B24" t="n">
-        <v>91981</v>
+        <v>79373</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2884,10 +2879,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>464412</v>
+        <v>464223</v>
       </c>
       <c r="R24" t="n">
-        <v>7073969</v>
+        <v>7074141</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2920,6 +2915,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 9057-2026 artfynd.xlsx
+++ b/artfynd/A 9057-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134215446</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134215450</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134215452</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134215453</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134215454</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134215455</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134215456</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134215457</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134215458</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134215459</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134215461</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134215449</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134215476</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134215447</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134215448</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2229,6 +2309,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134215467</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2331,6 +2416,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134215468</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2433,6 +2523,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134215469</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2535,6 +2630,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134215471</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2637,6 +2737,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134215472</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2739,6 +2844,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134215473</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2841,6 +2951,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134215474</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2943,8 +3058,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134215475</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>